--- a/Paper/_output/_comparison/crisis_analysis_variable_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_variable_yearly.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -453,18 +453,22 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,62 +539,82 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>hit_rate_full</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_full</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>hit_rate_ptt</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_ptt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>hit_rate_ttp</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_ttp</t>
         </is>
       </c>
     </row>
@@ -640,34 +664,34 @@
       <c r="M2" t="b">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>2250</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" s="3" t="n">
-        <v>-0.5233370252427398</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="3" t="n">
         <v>-0.5233370252427398</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="R2" s="3" t="n">
+        <v>-0.5233370252427398</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>888</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" s="3" t="n">
         <v>1.097918346834571</v>
       </c>
-      <c r="W2" s="3" t="inlineStr"/>
       <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" s="3" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -715,39 +739,51 @@
       <c r="M3" t="b">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>339</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" s="3" t="n">
-        <v>-0.5249389151859554</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" s="3" t="n">
         <v>-0.5249389151859554</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="R3" s="3" t="n">
+        <v>-0.5249389151859554</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>865</v>
       </c>
-      <c r="T3" t="n">
-        <v>-23</v>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" s="3" t="n">
         <v>1.104992456688879</v>
       </c>
-      <c r="W3" s="3" t="n">
+      <c r="X3" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="X3" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>0.5</v>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -796,39 +832,51 @@
       <c r="M4" t="b">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>2312</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" s="3" t="n">
-        <v>-0.5419801076228392</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" s="3" t="n">
         <v>-0.5419801076228392</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="R4" s="3" t="n">
+        <v>-0.5419801076228392</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>847</v>
       </c>
-      <c r="T4" t="n">
-        <v>-41</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" s="3" t="n">
         <v>1.183311285476965</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="X4" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>0.4</v>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -877,39 +925,51 @@
       <c r="M5" t="b">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>355</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" s="3" t="n">
-        <v>-0.4652359830536873</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
         <v>-0.4652359830536873</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="R5" s="3" t="n">
+        <v>-0.4652359830536873</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>744</v>
       </c>
-      <c r="T5" t="n">
-        <v>-144</v>
-      </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" s="3" t="n">
         <v>0.8699837092823588</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>0.6666666666666666</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="n">
         <v>0.6666666666666666</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -958,39 +1018,51 @@
       <c r="M6" t="b">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" t="n">
         <v>2240</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" s="3" t="n">
-        <v>-0.5178906786042018</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
         <v>-0.5178906786042018</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R6" s="3" t="n">
+        <v>-0.5178906786042018</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>883</v>
       </c>
-      <c r="T6" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" s="3" t="n">
         <v>1.07421834762458</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="X6" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>0.6</v>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1039,39 +1111,51 @@
       <c r="M7" t="b">
         <v>0</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" t="n">
         <v>2240</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" s="3" t="n">
-        <v>-0.5354812145044887</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" s="3" t="n">
         <v>-0.5354812145044887</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R7" s="3" t="n">
+        <v>-0.5354812145044887</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>1029</v>
       </c>
-      <c r="T7" t="n">
-        <v>141</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" s="3" t="n">
         <v>1.152765466596319</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="X7" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>0.4</v>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1120,39 +1204,51 @@
       <c r="M8" t="b">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>525</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" s="3" t="n">
-        <v>-0.4876150815614988</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
         <v>-0.4876150815614988</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R8" s="3" t="n">
+        <v>-0.4876150815614988</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>1244</v>
       </c>
-      <c r="T8" t="n">
-        <v>356</v>
-      </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" s="3" t="n">
         <v>0.9516577557503278</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="X8" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Y8" s="3" t="n">
-        <v>0.6666666666666666</v>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1166,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1180,17 +1276,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1251,55 +1350,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -1343,35 +1457,44 @@
       <c r="K2" s="3" t="n">
         <v>0.2657575172078715</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
+      <c r="L2" s="3" t="n">
+        <v>0.2657575172078715</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" s="3" t="n">
+        <v>-0.03939252582908814</v>
+      </c>
+      <c r="Q2" t="n">
         <v>583</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>-55</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="S2" s="3" t="n">
         <v>-0.4859401977791227</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.4862309442441404</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>1313</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="b">
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="Y2" s="3" t="n">
         <v>0.9452989626493449</v>
       </c>
     </row>
@@ -1415,35 +1538,42 @@
       <c r="K3" s="3" t="n">
         <v>0.181522378562615</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.1704176784565816</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>583</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>-55</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="S3" s="3" t="n">
         <v>-0.3995126785894293</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.4083924126510692</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>1088</v>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="b">
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="Y3" s="3" t="n">
         <v>0.6653140946439247</v>
       </c>
     </row>
@@ -1485,35 +1615,44 @@
       <c r="K4" s="3" t="n">
         <v>0.3183884110749757</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
+      <c r="L4" s="3" t="n">
+        <v>0.3183884110749757</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" s="3" t="n">
+        <v>-0.08522544924691133</v>
+      </c>
+      <c r="Q4" t="n">
         <v>583</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>-55</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>-0.5217486422257891</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.5311044950287367</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>1313</v>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="b">
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="Y4" s="3" t="n">
         <v>1.090950676343116</v>
       </c>
     </row>
@@ -1557,35 +1696,42 @@
       <c r="K5" s="3" t="n">
         <v>0.1468876731549894</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.1053602020059354</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>583</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>-55</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="S5" s="3" t="n">
         <v>-0.2967359307877762</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.3383158398603918</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>392</v>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="b">
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="Y5" s="3" t="n">
         <v>0.4219409803207652</v>
       </c>
     </row>
@@ -1627,35 +1773,44 @@
       <c r="K6" s="3" t="n">
         <v>0.2788179371039247</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
+      <c r="L6" s="3" t="n">
+        <v>0.2788179371039247</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
         <v>1</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" s="3" t="n">
+        <v>-0.02190491807181505</v>
+      </c>
+      <c r="Q6" t="n">
         <v>638</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.5046718081597298</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.5086484580604441</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>1258</v>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="b">
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="Y6" s="3" t="n">
         <v>1.018863485812802</v>
       </c>
     </row>
@@ -1697,35 +1852,44 @@
       <c r="K7" s="3" t="n">
         <v>0.2945323051586157</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
+      <c r="L7" s="3" t="n">
+        <v>0.2945323051586157</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" s="3" t="n">
+        <v>-0.03477373878520784</v>
+      </c>
+      <c r="Q7" t="n">
         <v>638</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.5165540962256929</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.522337027033672</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>1258</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="b">
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="Y7" s="3" t="n">
         <v>1.068483758354155</v>
       </c>
     </row>
@@ -1769,35 +1933,42 @@
       <c r="K8" s="3" t="n">
         <v>0.2522832883059996</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.2481939300735364</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>638</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.4816886905342953</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.4876150815614987</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>1197</v>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="b">
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="Y8" s="3" t="n">
         <v>0.9293424274898392</v>
       </c>
     </row>
@@ -1812,7 +1983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1826,17 +1997,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1897,55 +2071,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -1991,37 +2180,44 @@
       <c r="K2" s="3" t="n">
         <v>0.2354171526922748</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.2313619974770345</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>41186</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>355</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>-0.5035092528573142</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.5040024023286778</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>860</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>1.014136226616548</v>
       </c>
     </row>
@@ -2065,37 +2261,44 @@
       <c r="K3" s="3" t="n">
         <v>0.234474890875973</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.2308146618522344</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>41186</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>355</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.5243350442512891</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.5249389151859554</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>864</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>4</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>1.102320105600317</v>
       </c>
     </row>
@@ -2139,37 +2342,44 @@
       <c r="K4" s="3" t="n">
         <v>0.2376717026529739</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.2142409222656951</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>41186</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>355</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>-0.4884434813691406</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.4884434813691406</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>667</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>-193</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.9548182137849031</v>
       </c>
     </row>
@@ -2213,37 +2423,44 @@
       <c r="K5" s="3" t="n">
         <v>0.2062376999383152</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.1927753650054989</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>41186</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>355</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.4652359830536872</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.4652359830536872</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>744</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>-116</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.8699837092823584</v>
       </c>
     </row>
@@ -2287,37 +2504,44 @@
       <c r="K6" s="3" t="n">
         <v>0.2138272344349207</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.2097114897963909</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>41186</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>355</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.5031043706109166</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.5082988629979938</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>855</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>-5</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>1.012495061044242</v>
       </c>
     </row>
@@ -2361,37 +2585,44 @@
       <c r="K7" s="3" t="n">
         <v>0.2233719858597075</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.2233719858597075</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>41186</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>355</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.5129198176356868</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.514605350956002</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>903</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>43</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>1.053050064870114</v>
       </c>
     </row>
@@ -2435,37 +2666,44 @@
       <c r="K8" s="3" t="n">
         <v>0.1883773997556111</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.1765604781573983</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>41186</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>355</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.4706028507084904</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.4718154607749649</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>750</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>-110</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.8889410366835118</v>
       </c>
     </row>
@@ -2480,7 +2718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2494,17 +2732,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2565,55 +2806,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -2659,37 +2915,44 @@
       <c r="K2" s="3" t="n">
         <v>0.0826944425385638</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.08126610637298518</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>64</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>-0.195436869366569</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.202297991486007</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>76</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>0.2429105460160745</v>
       </c>
     </row>
@@ -2733,37 +2996,44 @@
       <c r="K3" s="3" t="n">
         <v>0.0617679826013454</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.05917515285219503</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>64</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.1706425815157273</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.1720264251314347</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>69</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>-7</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>0.2057527643842536</v>
       </c>
     </row>
@@ -2807,37 +3077,44 @@
       <c r="K4" s="3" t="n">
         <v>0.07584506561778721</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.07584506561778721</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>64</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>-0.191725710108013</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.1941024876751378</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>81</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>5</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.237203771672156</v>
       </c>
     </row>
@@ -2881,37 +3158,44 @@
       <c r="K5" s="3" t="n">
         <v>0.04836031164019643</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.04633029464080438</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>64</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.1464423397562973</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.1465009124724216</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>69</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>-7</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.1715670148335215</v>
       </c>
     </row>
@@ -2955,37 +3239,44 @@
       <c r="K6" s="3" t="n">
         <v>0.06490513107985459</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.05835036903888338</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>64</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.1690941297033365</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.1775169494986034</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>53</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>-23</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>0.2035057588929583</v>
       </c>
     </row>
@@ -3029,37 +3320,44 @@
       <c r="K7" s="3" t="n">
         <v>0.06770789437500559</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.06087008157747277</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>64</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.1755869558437451</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.1829503201425123</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>53</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>-23</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>0.2129842038385619</v>
       </c>
     </row>
@@ -3103,37 +3401,44 @@
       <c r="K8" s="3" t="n">
         <v>0.05755410775870121</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.05174172475350312</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>64</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.163574613865239</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.1652260547018463</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>53</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>-23</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.1955639039378518</v>
       </c>
     </row>
@@ -3148,7 +3453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3162,17 +3467,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3233,55 +3541,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -3327,37 +3650,44 @@
       <c r="K2" s="3" t="n">
         <v>0.1403286526425156</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.1124623994777716</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>23</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>-0.2902196151348784</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.2902196151348784</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>55</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>0.4088864968986545</v>
       </c>
     </row>
@@ -3401,37 +3731,44 @@
       <c r="K3" s="3" t="n">
         <v>0.1258815843555457</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.1238178120125459</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>23</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.3042808018588748</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.3042808018588748</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>95</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>40</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>0.4373615140589411</v>
       </c>
     </row>
@@ -3475,37 +3812,44 @@
       <c r="K4" s="3" t="n">
         <v>0.1312987302681535</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.1159961532416147</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>23</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>-0.3050371402068923</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.3050371402068923</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>72</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>17</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.438925815830939</v>
       </c>
     </row>
@@ -3549,37 +3893,44 @@
       <c r="K5" s="3" t="n">
         <v>0.1177175505348945</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.1177175505348945</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>23</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.2902464771828119</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.2902464771828119</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>99</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>44</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.4089398190385185</v>
       </c>
     </row>
@@ -3623,37 +3974,44 @@
       <c r="K6" s="3" t="n">
         <v>0.1334744213775015</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.1239077365635853</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>23</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.3111804093256711</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.3111804093256711</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>82</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>27</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>0.4517589417296293</v>
       </c>
     </row>
@@ -3697,37 +4055,44 @@
       <c r="K7" s="3" t="n">
         <v>0.1345453707542304</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.1249019264006729</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>23</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.3121003427249629</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.3121003427249629</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>82</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>27</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>0.4537003899104699</v>
       </c>
     </row>
@@ -3771,37 +4136,44 @@
       <c r="K8" s="3" t="n">
         <v>0.1310208562110952</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.1193130542934201</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>23</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.3019274392708716</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.3019274392708716</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>78</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>23</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.4325158389774153</v>
       </c>
     </row>
@@ -3816,7 +4188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3830,17 +4202,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3901,55 +4276,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -3995,37 +4385,44 @@
       <c r="K2" s="3" t="n">
         <v>0.1873955345996989</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.1760602304458135</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>253</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>58</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="S2" s="3" t="n">
         <v>-0.3239608533428747</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.3239608533428747</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>220</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>0.4792042812088539</v>
       </c>
     </row>
@@ -4069,37 +4466,44 @@
       <c r="K3" s="3" t="n">
         <v>0.1702003091096035</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.1397421712728002</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>195</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.2880125431936822</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.2880125431936822</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>166</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>-54</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>0.4045191252182836</v>
       </c>
     </row>
@@ -4143,37 +4547,44 @@
       <c r="K4" s="3" t="n">
         <v>0.1869460824536023</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.1869460824536023</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>297</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>102</v>
       </c>
-      <c r="P4" s="3" t="n">
+      <c r="S4" s="3" t="n">
         <v>-0.298221368786892</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.298221368786892</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>239</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>19</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.4249507686937986</v>
       </c>
     </row>
@@ -4217,37 +4628,44 @@
       <c r="K5" s="3" t="n">
         <v>0.1328475678049171</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.1123393940558932</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>195</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.2382824194485816</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.2382824194485816</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>188</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>-32</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.3128225283655466</v>
       </c>
     </row>
@@ -4291,37 +4709,44 @@
       <c r="K6" s="3" t="n">
         <v>0.1702187018471014</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.1350449913509219</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>195</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.2944579323458331</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.2944579323458331</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>142</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>-78</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>0.4173499297141365</v>
       </c>
     </row>
@@ -4365,37 +4790,44 @@
       <c r="K7" s="3" t="n">
         <v>0.1943317719820405</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.1571123143685358</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>195</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.3268135676014448</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.3268135676014448</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>155</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>-65</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>0.4854725999705787</v>
       </c>
     </row>
@@ -4439,37 +4871,44 @@
       <c r="K8" s="3" t="n">
         <v>0.1993947475706169</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.1614350761469678</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>195</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.324043264289569</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.324043264289569</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>156</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>-64</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.4793846220779194</v>
       </c>
     </row>
@@ -4484,7 +4923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4498,17 +4937,20 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="19" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4569,55 +5011,70 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>full_no_drawdown</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>full_not_recovered</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ptt_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ptt_days_vs_defined</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ptt_depth</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ptt_max_dd</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ptt_trough_at_boundary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ttp_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ttp_days_vs_bench</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ttp_vs_bench_censored</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ttp_return_to_even</t>
         </is>
@@ -4663,37 +5120,44 @@
       <c r="K2" s="3" t="n">
         <v>0.1032426212645815</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="L2" s="3" t="n">
+        <v>0.09381386490623618</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>34</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
         <v>-0.2242012270138071</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="T2" s="3" t="n">
         <v>-0.2242012270138071</v>
       </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>55</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="n">
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
         <v>0.2889940469367012</v>
       </c>
     </row>
@@ -4737,37 +5201,44 @@
       <c r="K3" s="3" t="n">
         <v>0.08555019016134056</v>
       </c>
-      <c r="L3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="L3" s="3" t="n">
+        <v>0.07944593068973861</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
         <v>34</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>-0.1844872203105785</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-0.1844872203105785</v>
       </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>59</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>4</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="n">
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
         <v>0.226222353475366</v>
       </c>
     </row>
@@ -4811,37 +5282,44 @@
       <c r="K4" s="3" t="n">
         <v>0.0982771437968664</v>
       </c>
-      <c r="L4" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="L4" s="3" t="n">
+        <v>0.08780088703966066</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
         <v>34</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>-0.2112316646811809</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="T4" s="3" t="n">
         <v>-0.2112316646811809</v>
       </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>52</v>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>-3</v>
       </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>0.2677993717836067</v>
       </c>
     </row>
@@ -4885,37 +5363,44 @@
       <c r="K5" s="3" t="n">
         <v>0.06372707386676911</v>
       </c>
-      <c r="L5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="L5" s="3" t="n">
+        <v>0.06372707386676911</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
         <v>34</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>-0.1556116196127491</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="T5" s="3" t="n">
         <v>-0.1556116196127491</v>
       </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>74</v>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>19</v>
       </c>
-      <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>0.184289153222813</v>
       </c>
     </row>
@@ -4959,37 +5444,44 @@
       <c r="K6" s="3" t="n">
         <v>0.09752257841525133</v>
       </c>
-      <c r="L6" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="L6" s="3" t="n">
+        <v>0.09480048048779645</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
         <v>34</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.2044491165694975</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="T6" s="3" t="n">
         <v>-0.2044491165694975</v>
       </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>68</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>13</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
         <v>0.2569906222564804</v>
       </c>
     </row>
@@ -5033,37 +5525,44 @@
       <c r="K7" s="3" t="n">
         <v>0.1010841009855249</v>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="L7" s="3" t="n">
+        <v>0.09387145096446046</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
         <v>34</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>-0.2083486754324958</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="T7" s="3" t="n">
         <v>-0.2083486754324958</v>
       </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>59</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>4</v>
       </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="n">
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
         <v>0.2631823745716855</v>
       </c>
     </row>
@@ -5107,37 +5606,44 @@
       <c r="K8" s="3" t="n">
         <v>0.08429914349524448</v>
       </c>
-      <c r="L8" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="L8" s="3" t="n">
+        <v>0.08352217628723528</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
         <v>34</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>-0.1878863304044792</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="T8" s="3" t="n">
         <v>-0.1878863304044792</v>
       </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>72</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>17</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>0.2313547197131374</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_variable_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_variable_yearly.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -882,12 +882,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -902,22 +902,22 @@
         <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40956</v>
+        <v>40582</v>
       </c>
       <c r="G5" t="n">
-        <v>1099</v>
+        <v>840</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.4652359830536873</v>
+        <v>-0.4019616742567396</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.4652359830536873</v>
+        <v>-0.4019616742567396</v>
       </c>
       <c r="J5" t="n">
-        <v>1098</v>
+        <v>839</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.2062376999383153</v>
+        <v>0.1774193046859526</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -931,21 +931,21 @@
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>-0.4652359830536873</v>
+        <v>-0.4019616742567396</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-0.4652359830536873</v>
+        <v>-0.4019616742567396</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>744</v>
+        <v>485</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
-        <v>0.8699837092823588</v>
+        <v>0.6721336358454439</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -989,28 +989,28 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>36623</v>
+        <v>39364</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>39881</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>41158</v>
+        <v>40956</v>
       </c>
       <c r="G6" t="n">
-        <v>3123</v>
+        <v>1099</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.5178906786042018</v>
+        <v>-0.4652359830536873</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.5178906786042018</v>
+        <v>-0.4652359830536873</v>
       </c>
       <c r="J6" t="n">
-        <v>3122</v>
+        <v>1098</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.259052176820844</v>
+        <v>0.2062376999383153</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -1020,60 +1020,60 @@
       </c>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>2240</v>
+        <v>355</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
-        <v>-0.5178906786042018</v>
+        <v>-0.4652359830536873</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.5178906786042018</v>
+        <v>-0.4652359830536873</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>883</v>
+        <v>744</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
-        <v>1.07421834762458</v>
+        <v>0.8699837092823588</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="Z6" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>4/6</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3/5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1088,22 +1088,22 @@
         <v>39881</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41374</v>
+        <v>41158</v>
       </c>
       <c r="G7" t="n">
-        <v>3269</v>
+        <v>3123</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.5354812145044887</v>
+        <v>-0.5178906786042018</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.5354812145044887</v>
+        <v>-0.5178906786042018</v>
       </c>
       <c r="J7" t="n">
-        <v>3268</v>
+        <v>3122</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2738434899737053</v>
+        <v>0.259052176820844</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -1117,21 +1117,21 @@
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" s="3" t="n">
-        <v>-0.5354812145044887</v>
+        <v>-0.5178906786042018</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-0.5354812145044887</v>
+        <v>-0.5178906786042018</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1029</v>
+        <v>883</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="3" t="n">
-        <v>1.152765466596319</v>
+        <v>1.07421834762458</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>0.5</v>
@@ -1142,31 +1142,31 @@
         </is>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>36770</v>
+        <v>36623</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>37538</v>
+        <v>39881</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>39344</v>
+        <v>41374</v>
       </c>
       <c r="G8" t="n">
-        <v>1769</v>
+        <v>3269</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.4876150815614988</v>
+        <v>-0.5354812145044887</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.4876150815614988</v>
+        <v>-0.5354812145044887</v>
       </c>
       <c r="J8" t="n">
-        <v>1768</v>
+        <v>3268</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2566520099333102</v>
+        <v>0.2738434899737053</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -1206,46 +1206,139 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>525</v>
+        <v>2240</v>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
-        <v>-0.4876150815614988</v>
+        <v>-0.5354812145044887</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>-0.4876150815614988</v>
+        <v>-0.5354812145044887</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1244</v>
+        <v>1029</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
+        <v>1.152765466596319</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>36770</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>39344</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1769</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-0.4876150815614988</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>-0.4876150815614988</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1768</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.2566520099333102</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>525</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" s="3" t="n">
+        <v>-0.4876150815614988</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>-0.4876150815614988</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1244</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" s="3" t="n">
         <v>0.9516577557503278</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X9" s="3" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>5/6</t>
         </is>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="Z9" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="AB8" s="3" t="n">
+      <c r="AB9" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
@@ -1262,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1659,12 +1752,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1679,25 +1772,25 @@
         <v>37460</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38028</v>
+        <v>37784</v>
       </c>
       <c r="G5" t="n">
-        <v>975</v>
+        <v>807</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.2092382282226474</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.3043384976802425</v>
       </c>
       <c r="J5" t="n">
-        <v>786</v>
+        <v>281</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1468876731549894</v>
+        <v>0.1174267585984309</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1053602020059354</v>
+        <v>0.07663710450244801</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>39364</v>
@@ -1716,34 +1809,34 @@
         <v>-55</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.2092382282226474</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.3043384976802425</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>392</v>
+        <v>224</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="b">
         <v>1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4219409803207652</v>
+        <v>0.2646033681577118</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1755,26 +1848,28 @@
         <v>36608</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
+        <v>37460</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>38028</v>
+      </c>
       <c r="G6" t="n">
-        <v>1896</v>
+        <v>975</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.5046718081597298</v>
+        <v>-0.2967359307877762</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="J6" t="n">
-        <v>1894</v>
+        <v>786</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.2788179371039247</v>
+        <v>0.1468876731549894</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2788179371039247</v>
+        <v>0.1053602020059354</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>39364</v>
@@ -1783,46 +1878,44 @@
         <v>0</v>
       </c>
       <c r="O6" t="b">
-        <v>1</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>-0.02190491807181505</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>638</v>
+        <v>583</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.5046718081597298</v>
+        <v>-0.2967359307877762</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1258</v>
+        <v>392</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="b">
         <v>1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>1.018863485812802</v>
+        <v>0.4219409803207652</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1841,19 +1934,19 @@
         <v>1896</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.5165540962256929</v>
+        <v>-0.5046718081597298</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="J7" t="n">
         <v>1894</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2945323051586157</v>
+        <v>0.2788179371039247</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2945323051586157</v>
+        <v>0.2788179371039247</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>39364</v>
@@ -1865,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>-0.03477373878520784</v>
+        <v>-0.02190491807181505</v>
       </c>
       <c r="Q7" t="n">
         <v>638</v>
@@ -1874,10 +1967,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.5165540962256929</v>
+        <v>-0.5046718081597298</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -1890,18 +1983,18 @@
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1.068483758354155</v>
+        <v>1.018863485812802</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1915,26 +2008,24 @@
       <c r="E8" s="2" t="n">
         <v>37538</v>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>39276</v>
-      </c>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>1835</v>
+        <v>1896</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.4816886905342953</v>
+        <v>-0.5165540962256929</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="J8" t="n">
-        <v>1827</v>
+        <v>1894</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2522832883059996</v>
+        <v>0.2945323051586157</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.2481939300735364</v>
+        <v>0.2945323051586157</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>39364</v>
@@ -1943,9 +2034,11 @@
         <v>0</v>
       </c>
       <c r="O8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>-0.03477373878520784</v>
+      </c>
       <c r="Q8" t="n">
         <v>638</v>
       </c>
@@ -1953,22 +2046,101 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.4816886905342953</v>
+        <v>-0.5165540962256929</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1197</v>
+        <v>1258</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="b">
         <v>1</v>
       </c>
       <c r="Y8" s="3" t="n">
+        <v>1.068483758354155</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>36608</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>39276</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1835</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-0.4816886905342953</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>-0.4876150815614987</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1827</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.2522832883059996</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.2481939300735364</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>638</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.4816886905342953</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.4876150815614987</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1197</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.9293424274898392</v>
       </c>
     </row>
@@ -1983,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2181,10 +2353,10 @@
         <v>0.2354171526922748</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.2313619974770345</v>
+        <v>0.1562892258388257</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>41186</v>
+        <v>43364</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -2262,10 +2434,10 @@
         <v>0.234474890875973</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2308146618522344</v>
+        <v>0.155919490696465</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>41186</v>
+        <v>43364</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -2343,10 +2515,10 @@
         <v>0.2376717026529739</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.2142409222656951</v>
+        <v>0.1447236289841644</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>41186</v>
+        <v>43364</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -2386,12 +2558,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2406,28 +2578,28 @@
         <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40956</v>
+        <v>40582</v>
       </c>
       <c r="G5" t="n">
-        <v>1099</v>
+        <v>840</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.4019616742567399</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.4019616742567399</v>
       </c>
       <c r="J5" t="n">
-        <v>1098</v>
+        <v>839</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.2062376999383152</v>
+        <v>0.177419304685953</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1927753650054989</v>
+        <v>0.09795419063977666</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>41186</v>
+        <v>43364</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -2443,36 +2615,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.4019616742567399</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.4019616742567399</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>744</v>
+        <v>485</v>
       </c>
       <c r="W5" t="n">
-        <v>-116</v>
+        <v>-375</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.8699837092823584</v>
+        <v>0.6721336358454448</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2487,28 +2659,28 @@
         <v>39881</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>41117</v>
+        <v>40956</v>
       </c>
       <c r="G6" t="n">
-        <v>1210</v>
+        <v>1099</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.5031043706109166</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="J6" t="n">
-        <v>1207</v>
+        <v>1098</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.2138272344349207</v>
+        <v>0.2062376999383152</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2097114897963909</v>
+        <v>0.1302232557034226</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>41186</v>
+        <v>43364</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -2524,36 +2696,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.5031043706109166</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>855</v>
+        <v>744</v>
       </c>
       <c r="W6" t="n">
-        <v>-5</v>
+        <v>-116</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>1.012495061044242</v>
+        <v>0.8699837092823584</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2568,28 +2740,28 @@
         <v>39881</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41186</v>
+        <v>41117</v>
       </c>
       <c r="G7" t="n">
-        <v>1258</v>
+        <v>1210</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.5129198176356868</v>
+        <v>-0.5031043706109166</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.514605350956002</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="J7" t="n">
-        <v>1255</v>
+        <v>1207</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2233719858597075</v>
+        <v>0.2138272344349207</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2233719858597075</v>
+        <v>0.1416639151943617</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>41186</v>
+        <v>43364</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -2605,36 +2777,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.5129198176356868</v>
+        <v>-0.5031043706109166</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.514605350956002</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>903</v>
+        <v>855</v>
       </c>
       <c r="W7" t="n">
-        <v>43</v>
+        <v>-5</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1.053050064870114</v>
+        <v>1.012495061044242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2649,28 +2821,28 @@
         <v>39881</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>40967</v>
+        <v>41186</v>
       </c>
       <c r="G8" t="n">
-        <v>1105</v>
+        <v>1258</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.4706028507084904</v>
+        <v>-0.5129198176356868</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.4718154607749649</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="J8" t="n">
-        <v>1103</v>
+        <v>1255</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1883773997556111</v>
+        <v>0.2233719858597075</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1765604781573983</v>
+        <v>0.1508918280650655</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>41186</v>
+        <v>43364</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -2686,24 +2858,105 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>-0.5129198176356868</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.514605350956002</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>903</v>
+      </c>
+      <c r="W8" t="n">
+        <v>43</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>1.053050064870114</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>39364</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>39881</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>40967</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1105</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>-0.4706028507084904</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>-0.4718154607749649</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="J9" t="n">
+        <v>1103</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.1883773997556111</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.1192698055249621</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>43364</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>355</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.4706028507084904</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.4718154607749649</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>750</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>-110</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.8889410366835118</v>
       </c>
     </row>
@@ -2718,7 +2971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2916,10 +3169,10 @@
         <v>0.0826944425385638</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.08126610637298518</v>
+        <v>0.05218963375687856</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>43578</v>
+        <v>43880</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -2997,10 +3250,10 @@
         <v>0.0617679826013454</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.05917515285219503</v>
+        <v>0.03800267654868232</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>43578</v>
+        <v>43880</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -3078,10 +3331,10 @@
         <v>0.07584506561778721</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.07584506561778721</v>
+        <v>0.04870820534567386</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>43578</v>
+        <v>43880</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -3121,12 +3374,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3141,28 +3394,28 @@
         <v>43458</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>43559</v>
+        <v>43563</v>
       </c>
       <c r="G5" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.138687252248779</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1434541510678393</v>
       </c>
       <c r="J5" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.04836031164019643</v>
+        <v>0.04842997312606301</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.04633029464080438</v>
+        <v>0.03001802059473596</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>43578</v>
+        <v>43880</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -3178,36 +3431,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.138687252248779</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1434541510678393</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="W5" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1715670148335215</v>
+        <v>0.1610184600319384</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3222,28 +3475,28 @@
         <v>43458</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>43537</v>
+        <v>43559</v>
       </c>
       <c r="G6" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="J6" t="n">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.06490513107985459</v>
+        <v>0.04836031164019643</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.05835036903888338</v>
+        <v>0.02975362321475319</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>43578</v>
+        <v>43880</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -3259,36 +3512,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="W6" t="n">
-        <v>-23</v>
+        <v>-7</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.2035057588929583</v>
+        <v>0.1715670148335215</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3309,22 +3562,22 @@
         <v>117</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.1690941297033365</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.1775169494986034</v>
       </c>
       <c r="J7" t="n">
         <v>107</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.06770789437500559</v>
+        <v>0.06490513107985459</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.06087008157747277</v>
+        <v>0.037472994900742</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>43578</v>
+        <v>43880</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -3340,10 +3593,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.1690941297033365</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.1775169494986034</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -3358,18 +3611,18 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2129842038385619</v>
+        <v>0.2035057588929583</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3390,22 +3643,22 @@
         <v>117</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.1755869558437451</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.1829503201425123</v>
       </c>
       <c r="J8" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.05755410775870121</v>
+        <v>0.06770789437500559</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.05174172475350312</v>
+        <v>0.03909117104367223</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>43578</v>
+        <v>43880</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -3421,10 +3674,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.1755869558437451</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.1829503201425123</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -3439,6 +3692,87 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
+        <v>0.2129842038385619</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>43364</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="G9" t="n">
+        <v>117</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>-0.163574613865239</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>-0.1652260547018463</v>
+      </c>
+      <c r="J9" t="n">
+        <v>114</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.05755410775870121</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.03322887960745487</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>64</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.163574613865239</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.1652260547018463</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>53</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-23</v>
+      </c>
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.1955639039378518</v>
       </c>
     </row>
@@ -3453,7 +3787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3651,10 +3985,10 @@
         <v>0.1403286526425156</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1124623994777716</v>
+        <v>0.05728893254440424</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>44055</v>
+        <v>44564</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -3732,10 +4066,10 @@
         <v>0.1258815843555457</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1238178120125459</v>
+        <v>0.06307343888376211</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>44055</v>
+        <v>44564</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -3813,10 +4147,10 @@
         <v>0.1312987302681535</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1159961532416147</v>
+        <v>0.05908904513265961</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>44055</v>
+        <v>44564</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -3856,12 +4190,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3882,22 +4216,22 @@
         <v>122</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422493289217</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422493289217</v>
       </c>
       <c r="J5" t="n">
         <v>121</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.1125125693043114</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.05731448931557177</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>44055</v>
+        <v>44564</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -3913,10 +4247,10 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422493289217</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2845422493289217</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -3931,18 +4265,18 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.3977065718584074</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3957,28 +4291,28 @@
         <v>43913</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>44032</v>
+        <v>44055</v>
       </c>
       <c r="G6" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="J6" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1334744213775015</v>
+        <v>0.1177175505348945</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1239077365635853</v>
+        <v>0.05996593388725459</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>44055</v>
+        <v>44564</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -3994,36 +4328,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="W6" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4517589417296293</v>
+        <v>0.4089398190385185</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4044,22 +4378,22 @@
         <v>105</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="J7" t="n">
         <v>104</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1345453707542304</v>
+        <v>0.1334744213775015</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1249019264006729</v>
+        <v>0.06311924691882544</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>44055</v>
+        <v>44564</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -4075,10 +4409,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -4093,18 +4427,18 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.4537003899104699</v>
+        <v>0.4517589417296293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4119,28 +4453,28 @@
         <v>43913</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>44026</v>
+        <v>44032</v>
       </c>
       <c r="G8" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="J8" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1310208562110952</v>
+        <v>0.1345453707542304</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1193130542934201</v>
+        <v>0.06362569240440749</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>44055</v>
+        <v>44564</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -4156,24 +4490,105 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>82</v>
+      </c>
+      <c r="W8" t="n">
+        <v>27</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.4537003899104699</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>44026</v>
+      </c>
+      <c r="G9" t="n">
+        <v>101</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>-0.3019274392708716</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>-0.3019274392708716</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="J9" t="n">
+        <v>100</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.1310208562110952</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.06077869181898075</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>23</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>78</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>23</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.4325158389774153</v>
       </c>
     </row>
@@ -4188,7 +4603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4386,10 +4801,10 @@
         <v>0.1873955345996989</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1760602304458135</v>
+        <v>0.1456175032694574</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45344</v>
+        <v>45707</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -4467,10 +4882,10 @@
         <v>0.1702003091096035</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1397421712728002</v>
+        <v>0.1155792312134959</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45344</v>
+        <v>45707</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -4548,10 +4963,10 @@
         <v>0.1869460824536023</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1869460824536023</v>
+        <v>0.1546210731632438</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>45344</v>
+        <v>45707</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -4591,12 +5006,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4611,28 +5026,28 @@
         <v>44846</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45121</v>
+        <v>45182</v>
       </c>
       <c r="G5" t="n">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="J5" t="n">
-        <v>382</v>
+        <v>424</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1328475678049171</v>
+        <v>0.135142485096232</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1123393940558932</v>
+        <v>0.09955472383307543</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>45344</v>
+        <v>45707</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -4648,36 +5063,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="W5" t="n">
-        <v>-32</v>
+        <v>10</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.3128225283655466</v>
+        <v>0.2960478980608379</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4692,28 +5107,28 @@
         <v>44846</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45054</v>
+        <v>45121</v>
       </c>
       <c r="G6" t="n">
-        <v>337</v>
+        <v>383</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="J6" t="n">
-        <v>336</v>
+        <v>382</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1702187018471014</v>
+        <v>0.1328475678049171</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1350449913509219</v>
+        <v>0.09291469197671884</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>45344</v>
+        <v>45707</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -4729,36 +5144,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="W6" t="n">
-        <v>-78</v>
+        <v>-32</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4173499297141365</v>
+        <v>0.3128225283655466</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4773,28 +5188,28 @@
         <v>44846</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45071</v>
+        <v>45054</v>
       </c>
       <c r="G7" t="n">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="J7" t="n">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1943317719820405</v>
+        <v>0.1702187018471014</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1571123143685358</v>
+        <v>0.1116942447466524</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>45344</v>
+        <v>45707</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -4810,36 +5225,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="W7" t="n">
-        <v>-65</v>
+        <v>-78</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.4854725999705787</v>
+        <v>0.4173499297141365</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4854,28 +5269,28 @@
         <v>44846</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45072</v>
+        <v>45071</v>
       </c>
       <c r="G8" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="J8" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1993947475706169</v>
+        <v>0.1943317719820405</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1614350761469678</v>
+        <v>0.1299458877981737</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>45344</v>
+        <v>45707</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -4891,24 +5306,105 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>155</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-65</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.4854725999705787</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>45072</v>
+      </c>
+      <c r="G9" t="n">
+        <v>351</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>-0.324043264289569</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>-0.324043264289569</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="J9" t="n">
+        <v>350</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.1993947475706169</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.1335211970875572</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>195</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>156</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>-64</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.4793846220779194</v>
       </c>
     </row>
@@ -4923,7 +5419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5121,10 +5617,10 @@
         <v>0.1032426212645815</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.09381386490623618</v>
+        <v>0.06633642004451827</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45863</v>
+        <v>46021</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -5202,10 +5698,10 @@
         <v>0.08555019016134056</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.07944593068973861</v>
+        <v>0.05617675632839062</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45863</v>
+        <v>46021</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -5283,10 +5779,10 @@
         <v>0.0982771437968664</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.08780088703966066</v>
+        <v>0.0620846026199381</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>45863</v>
+        <v>46021</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -5326,12 +5822,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5346,28 +5842,28 @@
         <v>45755</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45863</v>
+        <v>45910</v>
       </c>
       <c r="G5" t="n">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="J5" t="n">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.06372707386676911</v>
+        <v>0.0622368851691482</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.06372707386676911</v>
+        <v>0.05005289002890904</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>45863</v>
+        <v>46021</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -5383,36 +5879,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="W5" t="n">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.184289153222813</v>
+        <v>0.142957119009109</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5427,28 +5923,28 @@
         <v>45755</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45855</v>
+        <v>45863</v>
       </c>
       <c r="G6" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="J6" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.09752257841525133</v>
+        <v>0.06372707386676911</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.09480048048779645</v>
+        <v>0.04506184607636846</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>45863</v>
+        <v>46021</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -5464,36 +5960,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="W6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.2569906222564804</v>
+        <v>0.184289153222813</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5508,28 +6004,28 @@
         <v>45755</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45841</v>
+        <v>45855</v>
       </c>
       <c r="G7" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="J7" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1010841009855249</v>
+        <v>0.09752257841525133</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.09387145096446046</v>
+        <v>0.06703406261266386</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>45863</v>
+        <v>46021</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -5545,36 +6041,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="W7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2631823745716855</v>
+        <v>0.2569906222564804</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5589,28 +6085,28 @@
         <v>45755</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45861</v>
+        <v>45841</v>
       </c>
       <c r="G8" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.1878863304044792</v>
+        <v>-0.2083486754324958</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.1878863304044792</v>
+        <v>-0.2083486754324958</v>
       </c>
       <c r="J8" t="n">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.08429914349524448</v>
+        <v>0.1010841009855249</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.08352217628723528</v>
+        <v>0.06637713953679047</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>45863</v>
+        <v>46021</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -5626,24 +6122,105 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>-0.2083486754324958</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.2083486754324958</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>59</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.2631823745716855</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="G9" t="n">
+        <v>106</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>-0.1878863304044792</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>-0.1878863304044792</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
+      <c r="J9" t="n">
+        <v>105</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.08429914349524448</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.05905909723216233</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>34</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-0.1878863304044792</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-0.1878863304044792</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>72</v>
       </c>
-      <c r="W8" t="n">
+      <c r="W9" t="n">
         <v>17</v>
       </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="3" t="n">
+      <c r="X9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v>0.2313547197131374</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_variable_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_variable_yearly.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -882,12 +882,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -902,22 +902,22 @@
         <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40582</v>
+        <v>40956</v>
       </c>
       <c r="G5" t="n">
-        <v>840</v>
+        <v>1099</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.4652359830536873</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.4652359830536873</v>
       </c>
       <c r="J5" t="n">
-        <v>839</v>
+        <v>1098</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1774193046859526</v>
+        <v>0.2062376999383153</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -931,21 +931,21 @@
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" s="3" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.4652359830536873</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.4652359830536873</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>485</v>
+        <v>744</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
-        <v>0.6721336358454439</v>
+        <v>0.8699837092823588</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -989,28 +989,28 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>39364</v>
+        <v>36623</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>39881</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40956</v>
+        <v>41158</v>
       </c>
       <c r="G6" t="n">
-        <v>1099</v>
+        <v>3123</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.4652359830536873</v>
+        <v>-0.5178906786042018</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.4652359830536873</v>
+        <v>-0.5178906786042018</v>
       </c>
       <c r="J6" t="n">
-        <v>1098</v>
+        <v>3122</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.2062376999383153</v>
+        <v>0.259052176820844</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -1020,60 +1020,60 @@
       </c>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>355</v>
+        <v>2240</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" s="3" t="n">
-        <v>-0.4652359830536873</v>
+        <v>-0.5178906786042018</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.4652359830536873</v>
+        <v>-0.5178906786042018</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>744</v>
+        <v>883</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
-        <v>0.8699837092823588</v>
+        <v>1.07421834762458</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1088,22 +1088,22 @@
         <v>39881</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41158</v>
+        <v>41374</v>
       </c>
       <c r="G7" t="n">
-        <v>3123</v>
+        <v>3269</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.5178906786042018</v>
+        <v>-0.5354812145044887</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.5178906786042018</v>
+        <v>-0.5354812145044887</v>
       </c>
       <c r="J7" t="n">
-        <v>3122</v>
+        <v>3268</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.259052176820844</v>
+        <v>0.2738434899737053</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -1117,21 +1117,21 @@
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" s="3" t="n">
-        <v>-0.5178906786042018</v>
+        <v>-0.5354812145044887</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-0.5178906786042018</v>
+        <v>-0.5354812145044887</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>883</v>
+        <v>1029</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="3" t="n">
-        <v>1.07421834762458</v>
+        <v>1.152765466596319</v>
       </c>
       <c r="X7" s="3" t="n">
         <v>0.5</v>
@@ -1142,31 +1142,31 @@
         </is>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>36623</v>
+        <v>36770</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>39881</v>
+        <v>37538</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>41374</v>
+        <v>39344</v>
       </c>
       <c r="G8" t="n">
-        <v>3269</v>
+        <v>1769</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.5354812145044887</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.5354812145044887</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="J8" t="n">
-        <v>3268</v>
+        <v>1768</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2738434899737053</v>
+        <v>0.2566520099333102</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -1206,139 +1206,46 @@
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>2240</v>
+        <v>525</v>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" s="3" t="n">
-        <v>-0.5354812145044887</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>-0.5354812145044887</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1029</v>
+        <v>1244</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
-        <v>1.152765466596319</v>
+        <v>0.9516577557503278</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AC8" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>36770</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>39344</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1769</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.4876150815614988</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.4876150815614988</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1768</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.2566520099333102</v>
-      </c>
-      <c r="L9" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>525</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" s="3" t="n">
-        <v>-0.4876150815614988</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>-0.4876150815614988</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1244</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" s="3" t="n">
-        <v>0.9516577557503278</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AC9" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
@@ -1355,7 +1262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1752,12 +1659,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1772,25 +1679,25 @@
         <v>37460</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>37784</v>
+        <v>38028</v>
       </c>
       <c r="G5" t="n">
-        <v>807</v>
+        <v>975</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2092382282226474</v>
+        <v>-0.2967359307877762</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3043384976802425</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="J5" t="n">
-        <v>281</v>
+        <v>786</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1174267585984309</v>
+        <v>0.1468876731549894</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.07663710450244801</v>
+        <v>0.1053602020059354</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>39364</v>
@@ -1809,34 +1716,34 @@
         <v>-55</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2092382282226474</v>
+        <v>-0.2967359307877762</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.3043384976802425</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>224</v>
+        <v>392</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="b">
         <v>1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.2646033681577118</v>
+        <v>0.4219409803207652</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1848,28 +1755,26 @@
         <v>36608</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>38028</v>
-      </c>
+        <v>37538</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>975</v>
+        <v>1896</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.5046718081597298</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="J6" t="n">
-        <v>786</v>
+        <v>1894</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1468876731549894</v>
+        <v>0.2788179371039247</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1053602020059354</v>
+        <v>0.2788179371039247</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>39364</v>
@@ -1878,44 +1783,46 @@
         <v>0</v>
       </c>
       <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-0.02190491807181505</v>
+      </c>
       <c r="Q6" t="n">
-        <v>583</v>
+        <v>638</v>
       </c>
       <c r="R6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.5046718081597298</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>392</v>
+        <v>1258</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="b">
         <v>1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4219409803207652</v>
+        <v>1.018863485812802</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1934,19 +1841,19 @@
         <v>1896</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.5046718081597298</v>
+        <v>-0.5165540962256929</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="J7" t="n">
         <v>1894</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2788179371039247</v>
+        <v>0.2945323051586157</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2788179371039247</v>
+        <v>0.2945323051586157</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>39364</v>
@@ -1958,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>-0.02190491807181505</v>
+        <v>-0.03477373878520784</v>
       </c>
       <c r="Q7" t="n">
         <v>638</v>
@@ -1967,10 +1874,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.5046718081597298</v>
+        <v>-0.5165540962256929</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.522337027033672</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -1983,18 +1890,18 @@
         <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1.018863485812802</v>
+        <v>1.068483758354155</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2008,24 +1915,26 @@
       <c r="E8" s="2" t="n">
         <v>37538</v>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="n">
+        <v>39276</v>
+      </c>
       <c r="G8" t="n">
-        <v>1896</v>
+        <v>1835</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.5165540962256929</v>
+        <v>-0.4816886905342953</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.4876150815614987</v>
       </c>
       <c r="J8" t="n">
-        <v>1894</v>
+        <v>1827</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2945323051586157</v>
+        <v>0.2522832883059996</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.2945323051586157</v>
+        <v>0.2481939300735364</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>39364</v>
@@ -2034,11 +1943,9 @@
         <v>0</v>
       </c>
       <c r="O8" t="b">
-        <v>1</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>-0.03477373878520784</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
         <v>638</v>
       </c>
@@ -2046,101 +1953,22 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.5165540962256929</v>
+        <v>-0.4816886905342953</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.4876150815614987</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1258</v>
+        <v>1197</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="b">
         <v>1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.068483758354155</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>39276</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1835</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.4816886905342953</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.4876150815614987</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1827</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.2522832883059996</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.2481939300735364</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>638</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.4816886905342953</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.4876150815614987</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1197</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.9293424274898392</v>
       </c>
     </row>
@@ -2155,7 +1983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2558,12 +2386,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2578,25 +2406,25 @@
         <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40582</v>
+        <v>40956</v>
       </c>
       <c r="G5" t="n">
-        <v>840</v>
+        <v>1099</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="J5" t="n">
-        <v>839</v>
+        <v>1098</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.177419304685953</v>
+        <v>0.2062376999383152</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.09795419063977666</v>
+        <v>0.1302232557034226</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>43364</v>
@@ -2615,36 +2443,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>485</v>
+        <v>744</v>
       </c>
       <c r="W5" t="n">
-        <v>-375</v>
+        <v>-116</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.6721336358454448</v>
+        <v>0.8699837092823584</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2659,25 +2487,25 @@
         <v>39881</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>40956</v>
+        <v>41117</v>
       </c>
       <c r="G6" t="n">
-        <v>1099</v>
+        <v>1210</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.5031043706109166</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="J6" t="n">
-        <v>1098</v>
+        <v>1207</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.2062376999383152</v>
+        <v>0.2138272344349207</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1302232557034226</v>
+        <v>0.1416639151943617</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>43364</v>
@@ -2696,36 +2524,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.5031043706109166</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>744</v>
+        <v>855</v>
       </c>
       <c r="W6" t="n">
-        <v>-116</v>
+        <v>-5</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.8699837092823584</v>
+        <v>1.012495061044242</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2740,25 +2568,25 @@
         <v>39881</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>41117</v>
+        <v>41186</v>
       </c>
       <c r="G7" t="n">
-        <v>1210</v>
+        <v>1258</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.5031043706109166</v>
+        <v>-0.5129198176356868</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="J7" t="n">
-        <v>1207</v>
+        <v>1255</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2138272344349207</v>
+        <v>0.2233719858597075</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1416639151943617</v>
+        <v>0.1508918280650655</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>43364</v>
@@ -2777,36 +2605,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.5031043706109166</v>
+        <v>-0.5129198176356868</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>855</v>
+        <v>903</v>
       </c>
       <c r="W7" t="n">
-        <v>-5</v>
+        <v>43</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1.012495061044242</v>
+        <v>1.053050064870114</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2821,25 +2649,25 @@
         <v>39881</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>41186</v>
+        <v>40967</v>
       </c>
       <c r="G8" t="n">
-        <v>1258</v>
+        <v>1105</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.5129198176356868</v>
+        <v>-0.4706028507084904</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.514605350956002</v>
+        <v>-0.4718154607749649</v>
       </c>
       <c r="J8" t="n">
-        <v>1255</v>
+        <v>1103</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2233719858597075</v>
+        <v>0.1883773997556111</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1508918280650655</v>
+        <v>0.1192698055249621</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>43364</v>
@@ -2858,105 +2686,24 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.5129198176356868</v>
+        <v>-0.4706028507084904</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.514605350956002</v>
+        <v>-0.4718154607749649</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>903</v>
+        <v>750</v>
       </c>
       <c r="W8" t="n">
-        <v>43</v>
+        <v>-110</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.053050064870114</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>40967</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1105</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.4706028507084904</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.4718154607749649</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1103</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.1883773997556111</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.1192698055249621</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>355</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.4706028507084904</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.4718154607749649</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>750</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-110</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.8889410366835118</v>
       </c>
     </row>
@@ -2971,7 +2718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3374,12 +3121,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3394,25 +3141,25 @@
         <v>43458</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>43563</v>
+        <v>43559</v>
       </c>
       <c r="G5" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.138687252248779</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1434541510678393</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="J5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.04842997312606301</v>
+        <v>0.04836031164019643</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.03001802059473596</v>
+        <v>0.02975362321475319</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>43880</v>
@@ -3431,36 +3178,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.138687252248779</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1434541510678393</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="W5" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1610184600319384</v>
+        <v>0.1715670148335215</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3475,25 +3222,25 @@
         <v>43458</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>43559</v>
+        <v>43537</v>
       </c>
       <c r="G6" t="n">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.1690941297033365</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1775169494986034</v>
       </c>
       <c r="J6" t="n">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.04836031164019643</v>
+        <v>0.06490513107985459</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.02975362321475319</v>
+        <v>0.037472994900742</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>43880</v>
@@ -3512,36 +3259,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.1690941297033365</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1775169494986034</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="W6" t="n">
-        <v>-7</v>
+        <v>-23</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.1715670148335215</v>
+        <v>0.2035057588929583</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3562,19 +3309,19 @@
         <v>117</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.1755869558437451</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.1829503201425123</v>
       </c>
       <c r="J7" t="n">
         <v>107</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.06490513107985459</v>
+        <v>0.06770789437500559</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.037472994900742</v>
+        <v>0.03909117104367223</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>43880</v>
@@ -3593,10 +3340,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.1755869558437451</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.1829503201425123</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -3611,18 +3358,18 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2035057588929583</v>
+        <v>0.2129842038385619</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3643,19 +3390,19 @@
         <v>117</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.163574613865239</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.1652260547018463</v>
       </c>
       <c r="J8" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.06770789437500559</v>
+        <v>0.05755410775870121</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.03909117104367223</v>
+        <v>0.03322887960745487</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>43880</v>
@@ -3674,10 +3421,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.163574613865239</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.1652260547018463</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -3692,87 +3439,6 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.2129842038385619</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>43537</v>
-      </c>
-      <c r="G9" t="n">
-        <v>117</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.163574613865239</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.1652260547018463</v>
-      </c>
-      <c r="J9" t="n">
-        <v>114</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.05755410775870121</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.03322887960745487</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>64</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.163574613865239</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.1652260547018463</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>53</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-23</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.1955639039378518</v>
       </c>
     </row>
@@ -3787,7 +3453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4190,12 +3856,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4216,19 +3882,19 @@
         <v>122</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="J5" t="n">
         <v>121</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1125125693043114</v>
+        <v>0.1177175505348945</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.05731448931557177</v>
+        <v>0.05996593388725459</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>44564</v>
@@ -4247,10 +3913,10 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -4265,18 +3931,18 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.3977065718584074</v>
+        <v>0.4089398190385185</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4291,25 +3957,25 @@
         <v>43913</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>44055</v>
+        <v>44032</v>
       </c>
       <c r="G6" t="n">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="J6" t="n">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.1334744213775015</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.05996593388725459</v>
+        <v>0.06311924691882544</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>44564</v>
@@ -4328,36 +3994,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="W6" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.4517589417296293</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4378,19 +4044,19 @@
         <v>105</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="J7" t="n">
         <v>104</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1334744213775015</v>
+        <v>0.1345453707542304</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.06311924691882544</v>
+        <v>0.06362569240440749</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>44564</v>
@@ -4409,10 +4075,10 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -4427,18 +4093,18 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.4517589417296293</v>
+        <v>0.4537003899104699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4453,25 +4119,25 @@
         <v>43913</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>44032</v>
+        <v>44026</v>
       </c>
       <c r="G8" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="J8" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1345453707542304</v>
+        <v>0.1310208562110952</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.06362569240440749</v>
+        <v>0.06077869181898075</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>44564</v>
@@ -4490,105 +4156,24 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="W8" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.4537003899104699</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>44026</v>
-      </c>
-      <c r="G9" t="n">
-        <v>101</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="J9" t="n">
-        <v>100</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.1310208562110952</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.06077869181898075</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>23</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>78</v>
-      </c>
-      <c r="W9" t="n">
-        <v>23</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.4325158389774153</v>
       </c>
     </row>
@@ -4603,7 +4188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5006,12 +4591,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5026,25 +4611,25 @@
         <v>44846</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45182</v>
+        <v>45121</v>
       </c>
       <c r="G5" t="n">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="J5" t="n">
-        <v>424</v>
+        <v>382</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.135142485096232</v>
+        <v>0.1328475678049171</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.09955472383307543</v>
+        <v>0.09291469197671884</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>45707</v>
@@ -5063,36 +4648,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="W5" t="n">
-        <v>10</v>
+        <v>-32</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.2960478980608379</v>
+        <v>0.3128225283655466</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5107,25 +4692,25 @@
         <v>44846</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45121</v>
+        <v>45054</v>
       </c>
       <c r="G6" t="n">
-        <v>383</v>
+        <v>337</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="J6" t="n">
-        <v>382</v>
+        <v>336</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.1328475678049171</v>
+        <v>0.1702187018471014</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.09291469197671884</v>
+        <v>0.1116942447466524</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>45707</v>
@@ -5144,36 +4729,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2944579323458331</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="W6" t="n">
-        <v>-32</v>
+        <v>-78</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.3128225283655466</v>
+        <v>0.4173499297141365</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5188,25 +4773,25 @@
         <v>44846</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45054</v>
+        <v>45071</v>
       </c>
       <c r="G7" t="n">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="J7" t="n">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1702187018471014</v>
+        <v>0.1943317719820405</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1116942447466524</v>
+        <v>0.1299458877981737</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>45707</v>
@@ -5225,36 +4810,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3268135676014448</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="W7" t="n">
-        <v>-78</v>
+        <v>-65</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.4173499297141365</v>
+        <v>0.4854725999705787</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5269,25 +4854,25 @@
         <v>44846</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45071</v>
+        <v>45072</v>
       </c>
       <c r="G8" t="n">
+        <v>351</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="J8" t="n">
         <v>350</v>
       </c>
-      <c r="H8" s="3" t="n">
-        <v>-0.3268135676014448</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>-0.3268135676014448</v>
-      </c>
-      <c r="J8" t="n">
-        <v>349</v>
-      </c>
       <c r="K8" s="3" t="n">
-        <v>0.1943317719820405</v>
+        <v>0.1993947475706169</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.1299458877981737</v>
+        <v>0.1335211970875572</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>45707</v>
@@ -5306,105 +4891,24 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="W8" t="n">
-        <v>-65</v>
+        <v>-64</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.4854725999705787</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>45072</v>
-      </c>
-      <c r="G9" t="n">
-        <v>351</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="J9" t="n">
-        <v>350</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.1993947475706169</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.1335211970875572</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>195</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>156</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-64</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.4793846220779194</v>
       </c>
     </row>
@@ -5419,7 +4923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5822,12 +5326,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5842,25 +5346,25 @@
         <v>45755</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45910</v>
+        <v>45863</v>
       </c>
       <c r="G5" t="n">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="J5" t="n">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.0622368851691482</v>
+        <v>0.06372707386676911</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.05005289002890904</v>
+        <v>0.04506184607636846</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>46021</v>
@@ -5879,36 +5383,36 @@
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.1556116196127491</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="W5" t="n">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0.184289153222813</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5923,25 +5427,25 @@
         <v>45755</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45863</v>
+        <v>45855</v>
       </c>
       <c r="G6" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="J6" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.06372707386676911</v>
+        <v>0.09752257841525133</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.04506184607636846</v>
+        <v>0.06703406261266386</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>46021</v>
@@ -5960,36 +5464,36 @@
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2044491165694975</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="W6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.184289153222813</v>
+        <v>0.2569906222564804</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6004,25 +5508,25 @@
         <v>45755</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45855</v>
+        <v>45841</v>
       </c>
       <c r="G7" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.2083486754324958</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.2083486754324958</v>
       </c>
       <c r="J7" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.09752257841525133</v>
+        <v>0.1010841009855249</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.06703406261266386</v>
+        <v>0.06637713953679047</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>46021</v>
@@ -6041,36 +5545,36 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.2083486754324958</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.2044491165694975</v>
+        <v>-0.2083486754324958</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="W7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2569906222564804</v>
+        <v>0.2631823745716855</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6085,25 +5589,25 @@
         <v>45755</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45841</v>
+        <v>45861</v>
       </c>
       <c r="G8" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.1878863304044792</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.1878863304044792</v>
       </c>
       <c r="J8" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.1010841009855249</v>
+        <v>0.08429914349524448</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.06637713953679047</v>
+        <v>0.05905909723216233</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>46021</v>
@@ -6122,105 +5626,24 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.1878863304044792</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.2083486754324958</v>
+        <v>-0.1878863304044792</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="W8" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.2631823745716855</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>45861</v>
-      </c>
-      <c r="G9" t="n">
-        <v>106</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>-0.1878863304044792</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>-0.1878863304044792</v>
-      </c>
-      <c r="J9" t="n">
-        <v>105</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0.08429914349524448</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.05905909723216233</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>34</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-0.1878863304044792</v>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>-0.1878863304044792</v>
-      </c>
-      <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>72</v>
-      </c>
-      <c r="W9" t="n">
-        <v>17</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>0.2313547197131374</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_variable_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_variable_yearly.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -762,27 +763,27 @@
         <v>1.104992456688879</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -855,27 +856,27 @@
         <v>1.183311285476965</v>
       </c>
       <c r="X4" s="3" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3/7</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>3/6</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2/5</t>
         </is>
       </c>
     </row>
@@ -948,27 +949,27 @@
         <v>0.8699837092823588</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1041,27 +1042,27 @@
         <v>1.07421834762458</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="Z6" s="3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>4/6</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3/5</t>
         </is>
       </c>
     </row>
@@ -1134,27 +1135,27 @@
         <v>1.152765466596319</v>
       </c>
       <c r="X7" s="3" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3/7</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2/7</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>3/6</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2/5</t>
         </is>
       </c>
     </row>
@@ -1227,27 +1228,27 @@
         <v>0.9516577557503278</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1436,66 +1437,68 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="G2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>-0.4859401977791227</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="J2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.2657575172078715</v>
+        <v>0.09032004823014485</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.2657575172078715</v>
+        <v>0.04076898034342919</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
       <c r="O2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>-0.03939252582908814</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="R2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.4859401977791227</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.9452989626493449</v>
+        <v>0.204425521991354</v>
       </c>
     </row>
     <row r="3">
@@ -1515,34 +1518,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>39035</v>
+        <v>36116</v>
       </c>
       <c r="G3" t="n">
-        <v>1671</v>
+        <v>86</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-0.3995126785894293</v>
+        <v>-0.1732838894298508</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>-0.4083924126510692</v>
+        <v>-0.1750807802290463</v>
       </c>
       <c r="J3" t="n">
-        <v>1656</v>
+        <v>84</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.181522378562615</v>
+        <v>0.09341206331728004</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1704176784565816</v>
+        <v>0.04216466496471939</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -1552,29 +1555,31 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="R3" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.3995126785894293</v>
+        <v>-0.1732838894298508</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.4083924126510692</v>
+        <v>-0.1750807802290463</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1088</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
       <c r="X3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.6653140946439247</v>
+        <v>0.2096050714559616</v>
       </c>
     </row>
     <row r="4">
@@ -1594,66 +1599,68 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
+        <v>36076</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>36117</v>
+      </c>
       <c r="G4" t="n">
-        <v>1896</v>
+        <v>87</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-0.5217486422257891</v>
+        <v>-0.1945080942039396</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="J4" t="n">
-        <v>1889</v>
+        <v>85</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.3183884110749757</v>
+        <v>0.1007681391452584</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.3183884110749757</v>
+        <v>0.04574573788463201</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>-0.08522544924691133</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>583</v>
+        <v>58</v>
       </c>
       <c r="R4" t="n">
-        <v>-55</v>
+        <v>27</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.5217486422257891</v>
+        <v>-0.1945080942039396</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.5311044950287367</v>
+        <v>-0.1972105844421849</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1313</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-26</v>
+      </c>
       <c r="X4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1.090950676343116</v>
+        <v>0.2414774038129024</v>
       </c>
     </row>
     <row r="5">
@@ -1673,34 +1680,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38028</v>
+        <v>36105</v>
       </c>
       <c r="G5" t="n">
-        <v>975</v>
+        <v>79</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="J5" t="n">
-        <v>786</v>
+        <v>78</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.1468876731549894</v>
+        <v>0.08993390447450868</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1053602020059354</v>
+        <v>0.03892731995262652</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1710,29 +1717,31 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="R5" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>392</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-7</v>
+      </c>
       <c r="X5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4219409803207652</v>
+        <v>0.1946904599376615</v>
       </c>
     </row>
     <row r="6">
@@ -1752,66 +1761,68 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>36115</v>
+      </c>
       <c r="G6" t="n">
-        <v>1896</v>
+        <v>85</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.5046718081597298</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="J6" t="n">
-        <v>1894</v>
+        <v>83</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.2788179371039247</v>
+        <v>0.1002859776838859</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2788179371039247</v>
+        <v>0.04500652696670188</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
       </c>
       <c r="O6" t="b">
-        <v>1</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>-0.02190491807181505</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.5046718081597298</v>
+        <v>-0.1801116697737415</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.5086484580604441</v>
+        <v>-0.1858856338605598</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1258</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1</v>
+      </c>
       <c r="X6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>1.018863485812802</v>
+        <v>0.2196782941452984</v>
       </c>
     </row>
     <row r="7">
@@ -1831,66 +1842,68 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>37538</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>36105</v>
+      </c>
       <c r="G7" t="n">
-        <v>1896</v>
+        <v>79</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.5165540962256929</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="J7" t="n">
-        <v>1894</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2945323051586157</v>
+        <v>0.09791080322851566</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2945323051586157</v>
+        <v>0.04238006996766621</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
       </c>
       <c r="O7" t="b">
-        <v>1</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>-0.03477373878520784</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.5165540962256929</v>
+        <v>-0.1760081665685741</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.522337027033672</v>
+        <v>-0.1822275786451527</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1258</v>
-      </c>
-      <c r="W7" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-7</v>
+      </c>
       <c r="X7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1.068483758354155</v>
+        <v>0.2136042609009934</v>
       </c>
     </row>
     <row r="8">
@@ -1910,34 +1923,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>39276</v>
+        <v>36105</v>
       </c>
       <c r="G8" t="n">
-        <v>1835</v>
+        <v>79</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.4816886905342953</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="J8" t="n">
-        <v>1827</v>
+        <v>77</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.2522832883059996</v>
+        <v>0.09666256119913624</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.2481939300735364</v>
+        <v>0.04183977632490837</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -1947,29 +1960,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.4816886905342953</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1197</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-7</v>
+      </c>
       <c r="X8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.9293424274898392</v>
+        <v>0.2116308787151915</v>
       </c>
     </row>
   </sheetData>
@@ -2157,68 +2172,66 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>-0.4862309442441404</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-0.4862309442441404</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.2658275917027499</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.2658275917027499</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>-0.5035092528573142</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>-0.5040024023286778</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.2354171526922748</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.1562892258388257</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
       <c r="O2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>-0.03993583465459449</v>
+      </c>
       <c r="Q2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.5035092528573142</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>860</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>1.014136226616548</v>
+        <v>0.9463998245842093</v>
       </c>
     </row>
     <row r="3">
@@ -2238,34 +2251,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>39035</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1670</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.3982782035395848</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.408392412651069</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1652</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.181576604990091</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.1704625379155431</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>41130</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1219</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>-0.5243350442512891</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>-0.5249389151859554</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1217</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.234474890875973</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.155919490696465</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -2275,31 +2288,29 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.5243350442512891</v>
+        <v>-0.3982782035395848</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.5249389151859554</v>
+        <v>-0.408392412651069</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>864</v>
-      </c>
-      <c r="W3" t="n">
-        <v>4</v>
-      </c>
+        <v>1088</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>1.102320105600317</v>
+        <v>0.6618975843694335</v>
       </c>
     </row>
     <row r="4">
@@ -2319,68 +2330,66 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1895</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.5248897185497376</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-0.5311044950287365</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1893</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.3184723631953733</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.3184723631953733</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>40843</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1022</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-0.4884434813691406</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>-0.4884434813691406</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1021</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.2376717026529739</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.1447236289841644</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>-0.09123353816587243</v>
+      </c>
       <c r="Q4" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.4884434813691406</v>
+        <v>-0.5248897185497376</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.4884434813691406</v>
+        <v>-0.5311044950287365</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>667</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-193</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.9548182137849031</v>
+        <v>1.104774489298621</v>
       </c>
     </row>
     <row r="5">
@@ -2400,34 +2409,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>38028</v>
+      </c>
+      <c r="G5" t="n">
+        <v>974</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.2951492679396009</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.3383158398603918</v>
+      </c>
+      <c r="J5" t="n">
+        <v>769</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.1469627184408073</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.1053877950228616</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>40956</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1099</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>-0.4652359830536872</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>-0.4652359830536872</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1098</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.2062376999383152</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.1302232557034226</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -2437,31 +2446,29 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.2951492679396009</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>744</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-116</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.8699837092823584</v>
+        <v>0.4187401027120015</v>
       </c>
     </row>
     <row r="6">
@@ -2481,68 +2488,66 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>1895</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.5038864433233317</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.5086484580604441</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1893</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.2788914529787295</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.2788914529787295</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>41117</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1210</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>-0.5031043706109166</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>-0.5082988629979938</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1207</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.2138272344349207</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.1416639151943617</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="N6" t="b">
         <v>0</v>
       </c>
       <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-0.02035410490055889</v>
+      </c>
       <c r="Q6" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.5031043706109166</v>
+        <v>-0.5038864433233317</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.5082988629979938</v>
+        <v>-0.5086484580604441</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>855</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-5</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>1.012495061044242</v>
+        <v>1.015667555425681</v>
       </c>
     </row>
     <row r="7">
@@ -2562,68 +2567,66 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-0.5164822477237522</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.522337027033672</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1893</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.2946099669213893</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.2946099669213893</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>41186</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>-0.03463028931059076</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>637</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-0.5164822477237522</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-0.522337027033672</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>1258</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>-0.5129198176356868</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>-0.514605350956002</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1255</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.2233719858597075</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.1508918280650655</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" t="n">
-        <v>355</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>-0.5129198176356868</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>-0.514605350956002</v>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>903</v>
-      </c>
-      <c r="W7" t="n">
-        <v>43</v>
-      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>1.053050064870114</v>
+        <v>1.068176391233451</v>
       </c>
     </row>
     <row r="8">
@@ -2643,34 +2646,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>39276</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1834</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.480465778751608</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.4876150815614988</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1823</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.2523520150009724</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.2482593675457558</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>40967</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1105</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>-0.4706028507084904</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>-0.4718154607749649</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1103</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.1883773997556111</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.1192698055249621</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -2680,31 +2683,29 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.4706028507084904</v>
+        <v>-0.480465778751608</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.4718154607749649</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>750</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-110</v>
-      </c>
+        <v>1197</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.8889410366835118</v>
+        <v>0.9248010219559624</v>
       </c>
     </row>
   </sheetData>
@@ -2892,34 +2893,34 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="G2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573142</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="J2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.0826944425385638</v>
+        <v>0.2354171526922748</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.05218963375687856</v>
+        <v>0.1563175570682506</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -2929,22 +2930,22 @@
       </c>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573142</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -2953,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.2429105460160745</v>
+        <v>1.014136226616548</v>
       </c>
     </row>
     <row r="3">
@@ -2973,34 +2974,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>43559</v>
+        <v>41130</v>
       </c>
       <c r="G3" t="n">
-        <v>133</v>
+        <v>1219</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-0.1706425815157273</v>
+        <v>-0.5243350442512891</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>-0.1720264251314347</v>
+        <v>-0.5249389151859554</v>
       </c>
       <c r="J3" t="n">
-        <v>131</v>
+        <v>1217</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.0617679826013454</v>
+        <v>0.234474890875973</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.03800267654868232</v>
+        <v>0.1559477549023886</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -3010,31 +3011,31 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.1706425815157273</v>
+        <v>-0.5243350442512891</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.1720264251314347</v>
+        <v>-0.5249389151859554</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>69</v>
+        <v>864</v>
       </c>
       <c r="W3" t="n">
-        <v>-7</v>
+        <v>4</v>
       </c>
       <c r="X3" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.2057527643842536</v>
+        <v>1.102320105600317</v>
       </c>
     </row>
     <row r="4">
@@ -3054,34 +3055,34 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>43578</v>
+        <v>40843</v>
       </c>
       <c r="G4" t="n">
-        <v>145</v>
+        <v>1022</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.4884434813691406</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.4884434813691406</v>
       </c>
       <c r="J4" t="n">
-        <v>140</v>
+        <v>1021</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.07584506561778721</v>
+        <v>0.2376717026529739</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.04870820534567386</v>
+        <v>0.1447498636674188</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -3091,31 +3092,31 @@
       </c>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.191725710108013</v>
+        <v>-0.4884434813691406</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.1941024876751378</v>
+        <v>-0.4884434813691406</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>81</v>
+        <v>667</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>-193</v>
       </c>
       <c r="X4" t="b">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.237203771672156</v>
+        <v>0.9548182137849031</v>
       </c>
     </row>
     <row r="5">
@@ -3135,34 +3136,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>43559</v>
+        <v>40956</v>
       </c>
       <c r="G5" t="n">
-        <v>133</v>
+        <v>1099</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="J5" t="n">
-        <v>131</v>
+        <v>1098</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.04836031164019643</v>
+        <v>0.2062376999383152</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.02975362321475319</v>
+        <v>0.1302468618407874</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -3172,31 +3173,31 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>69</v>
+        <v>744</v>
       </c>
       <c r="W5" t="n">
-        <v>-7</v>
+        <v>-116</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.1715670148335215</v>
+        <v>0.8699837092823584</v>
       </c>
     </row>
     <row r="6">
@@ -3216,34 +3217,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>43537</v>
+        <v>41117</v>
       </c>
       <c r="G6" t="n">
-        <v>117</v>
+        <v>1210</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.5031043706109166</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="J6" t="n">
-        <v>107</v>
+        <v>1207</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.06490513107985459</v>
+        <v>0.2138272344349207</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.037472994900742</v>
+        <v>0.1416895952299563</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -3253,31 +3254,31 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.1690941297033365</v>
+        <v>-0.5031043706109166</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.1775169494986034</v>
+        <v>-0.5082988629979938</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>53</v>
+        <v>855</v>
       </c>
       <c r="W6" t="n">
-        <v>-23</v>
+        <v>-5</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.2035057588929583</v>
+        <v>1.012495061044242</v>
       </c>
     </row>
     <row r="7">
@@ -3297,34 +3298,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>43537</v>
+        <v>41186</v>
       </c>
       <c r="G7" t="n">
-        <v>117</v>
+        <v>1258</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.5129198176356868</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="J7" t="n">
-        <v>107</v>
+        <v>1255</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.06770789437500559</v>
+        <v>0.2233719858597075</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.03909117104367223</v>
+        <v>0.1509191808846621</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -3334,31 +3335,31 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.1755869558437451</v>
+        <v>-0.5129198176356868</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.1829503201425123</v>
+        <v>-0.514605350956002</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>53</v>
+        <v>903</v>
       </c>
       <c r="W7" t="n">
-        <v>-23</v>
+        <v>43</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.2129842038385619</v>
+        <v>1.053050064870114</v>
       </c>
     </row>
     <row r="8">
@@ -3378,34 +3379,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>43537</v>
+        <v>40967</v>
       </c>
       <c r="G8" t="n">
-        <v>117</v>
+        <v>1105</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4706028507084904</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4718154607749649</v>
       </c>
       <c r="J8" t="n">
-        <v>114</v>
+        <v>1103</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.05755410775870121</v>
+        <v>0.1883773997556111</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.03322887960745487</v>
+        <v>0.1192914260826535</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -3415,31 +3416,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4706028507084904</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4718154607749649</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>53</v>
+        <v>750</v>
       </c>
       <c r="W8" t="n">
-        <v>-23</v>
+        <v>-110</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.1955639039378518</v>
+        <v>0.8889410366835118</v>
       </c>
     </row>
   </sheetData>
@@ -3627,34 +3628,34 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="G2" t="n">
+        <v>143</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>-0.1989728318606707</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-0.202297991486007</v>
+      </c>
+      <c r="J2" t="n">
+        <v>138</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.08183226369428304</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.0521184671904906</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="G2" t="n">
-        <v>78</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="J2" t="n">
-        <v>77</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.1403286526425156</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.05728893254440424</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -3664,22 +3665,22 @@
       </c>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606707</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -3688,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.4088864968986545</v>
+        <v>0.2483971078320051</v>
       </c>
     </row>
     <row r="3">
@@ -3708,34 +3709,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="G3" t="n">
+        <v>134</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.1721376387087035</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.1721376387087035</v>
+      </c>
+      <c r="J3" t="n">
+        <v>133</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.06164770299751944</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.03801627907263108</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>44049</v>
-      </c>
-      <c r="G3" t="n">
-        <v>118</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>-0.3042808018588748</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>-0.3042808018588748</v>
-      </c>
-      <c r="J3" t="n">
-        <v>117</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.1258815843555457</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.06307343888376211</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -3745,31 +3746,31 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.3042808018588748</v>
+        <v>-0.1721376387087035</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.3042808018588748</v>
+        <v>-0.1721376387087035</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="W3" t="n">
-        <v>40</v>
+        <v>-9</v>
       </c>
       <c r="X3" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.4373615140589411</v>
+        <v>0.2079302632386908</v>
       </c>
     </row>
     <row r="4">
@@ -3789,34 +3790,34 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="G4" t="n">
+        <v>146</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.1935462542088221</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-0.1941024876751378</v>
+      </c>
+      <c r="J4" t="n">
+        <v>144</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.07558961362210245</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.04864146159510002</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>44018</v>
-      </c>
-      <c r="G4" t="n">
-        <v>95</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>-0.3050371402068923</v>
-      </c>
-      <c r="J4" t="n">
-        <v>94</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.1312987302681535</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.05908904513265961</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -3826,31 +3827,31 @@
       </c>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1935462542088221</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.3050371402068923</v>
+        <v>-0.1941024876751378</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="W4" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="X4" t="b">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.438925815830939</v>
+        <v>0.2399967204801585</v>
       </c>
     </row>
     <row r="5">
@@ -3870,34 +3871,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="G5" t="n">
+        <v>134</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.1461536977865012</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.1465009124724216</v>
+      </c>
+      <c r="J5" t="n">
+        <v>130</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.04818086645128587</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.02971168714991625</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="G5" t="n">
-        <v>122</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="J5" t="n">
-        <v>121</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.1177175505348945</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.05996593388725459</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -3907,31 +3908,31 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="W5" t="n">
-        <v>44</v>
+        <v>-9</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1711709676643378</v>
       </c>
     </row>
     <row r="6">
@@ -3951,34 +3952,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="G6" t="n">
+        <v>118</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.1712229343499421</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.1775169494986033</v>
+      </c>
+      <c r="J6" t="n">
+        <v>111</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.06463413170556485</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.03742150269784624</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="G6" t="n">
-        <v>105</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>-0.3111804093256711</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>-0.3111804093256711</v>
-      </c>
-      <c r="J6" t="n">
-        <v>104</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.1334744213775015</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.06311924691882544</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -3988,31 +3989,31 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1712229343499421</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.3111804093256711</v>
+        <v>-0.1775169494986033</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="W6" t="n">
-        <v>27</v>
+        <v>-25</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4517589417296293</v>
+        <v>0.2065970952220328</v>
       </c>
     </row>
     <row r="7">
@@ -4032,34 +4033,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="G7" t="n">
+        <v>118</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-0.1781636276426458</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.1829503201425124</v>
+      </c>
+      <c r="J7" t="n">
+        <v>114</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.06742645627613136</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.03903818692788627</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>44032</v>
-      </c>
-      <c r="G7" t="n">
-        <v>105</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>-0.3121003427249629</v>
-      </c>
-      <c r="J7" t="n">
-        <v>104</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.1345453707542304</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.06362569240440749</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -4069,31 +4070,31 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1781636276426458</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3121003427249629</v>
+        <v>-0.1829503201425124</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="W7" t="n">
-        <v>27</v>
+        <v>-25</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.4537003899104699</v>
+        <v>0.2167872263083241</v>
       </c>
     </row>
     <row r="8">
@@ -4113,34 +4114,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="G8" t="n">
+        <v>118</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.1639593569865845</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.1652260547018464</v>
+      </c>
+      <c r="J8" t="n">
+        <v>115</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.0573135221947752</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.03318305775662167</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>44026</v>
-      </c>
-      <c r="G8" t="n">
-        <v>101</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="J8" t="n">
-        <v>100</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.1310208562110952</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.06077869181898075</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -4150,31 +4151,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1639593569865845</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>-25</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.4325158389774153</v>
+        <v>0.196114098467284</v>
       </c>
     </row>
   </sheetData>
@@ -4362,34 +4363,34 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="G2" t="n">
+        <v>78</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="J2" t="n">
+        <v>77</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.1403286526425156</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.05728893254440424</v>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="G2" t="n">
-        <v>473</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>-0.3239608533428747</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>-0.3239608533428747</v>
-      </c>
-      <c r="J2" t="n">
-        <v>472</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.1873955345996989</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.1456175032694574</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -4399,22 +4400,22 @@
       </c>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="R2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -4423,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.4792042812088539</v>
+        <v>0.4088864968986545</v>
       </c>
     </row>
     <row r="3">
@@ -4443,34 +4444,34 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>44049</v>
+      </c>
+      <c r="G3" t="n">
+        <v>118</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.3042808018588748</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.3042808018588748</v>
+      </c>
+      <c r="J3" t="n">
+        <v>117</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.1258815843555457</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.06307343888376211</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>45089</v>
-      </c>
-      <c r="G3" t="n">
-        <v>361</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>-0.2880125431936822</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>-0.2880125431936822</v>
-      </c>
-      <c r="J3" t="n">
-        <v>360</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.1702003091096035</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.1155792312134959</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -4480,31 +4481,31 @@
       </c>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>-0.2880125431936822</v>
+        <v>-0.3042808018588748</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>-0.2880125431936822</v>
+        <v>-0.3042808018588748</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="W3" t="n">
-        <v>-54</v>
+        <v>40</v>
       </c>
       <c r="X3" t="b">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.4045191252182836</v>
+        <v>0.4373615140589411</v>
       </c>
     </row>
     <row r="4">
@@ -4524,34 +4525,34 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>44018</v>
+      </c>
+      <c r="G4" t="n">
+        <v>95</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-0.3050371402068923</v>
+      </c>
+      <c r="J4" t="n">
+        <v>94</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.1312987302681535</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.05908904513265961</v>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>45344</v>
-      </c>
-      <c r="G4" t="n">
-        <v>536</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-0.298221368786892</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>-0.298221368786892</v>
-      </c>
-      <c r="J4" t="n">
-        <v>535</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0.1869460824536023</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.1546210731632438</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -4561,31 +4562,31 @@
       </c>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>297</v>
+        <v>23</v>
       </c>
       <c r="R4" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.298221368786892</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-0.298221368786892</v>
+        <v>-0.3050371402068923</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>239</v>
+        <v>72</v>
       </c>
       <c r="W4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="X4" t="b">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.4249507686937986</v>
+        <v>0.438925815830939</v>
       </c>
     </row>
     <row r="5">
@@ -4605,34 +4606,34 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="G5" t="n">
+        <v>122</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="J5" t="n">
+        <v>121</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.1177175505348945</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.05996593388725459</v>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>45121</v>
-      </c>
-      <c r="G5" t="n">
-        <v>383</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>-0.2382824194485816</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>-0.2382824194485816</v>
-      </c>
-      <c r="J5" t="n">
-        <v>382</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.1328475678049171</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.09291469197671884</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -4642,31 +4643,31 @@
       </c>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="W5" t="n">
-        <v>-32</v>
+        <v>44</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.3128225283655466</v>
+        <v>0.4089398190385185</v>
       </c>
     </row>
     <row r="6">
@@ -4686,34 +4687,34 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="G6" t="n">
+        <v>105</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.3111804093256711</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.3111804093256711</v>
+      </c>
+      <c r="J6" t="n">
+        <v>104</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.1334744213775015</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.06311924691882544</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>45054</v>
-      </c>
-      <c r="G6" t="n">
-        <v>337</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>-0.2944579323458331</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>-0.2944579323458331</v>
-      </c>
-      <c r="J6" t="n">
-        <v>336</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.1702187018471014</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.1116942447466524</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -4723,31 +4724,31 @@
       </c>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-0.2944579323458331</v>
+        <v>-0.3111804093256711</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="W6" t="n">
-        <v>-78</v>
+        <v>27</v>
       </c>
       <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.4173499297141365</v>
+        <v>0.4517589417296293</v>
       </c>
     </row>
     <row r="7">
@@ -4767,34 +4768,34 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>44032</v>
+      </c>
+      <c r="G7" t="n">
+        <v>105</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.3121003427249629</v>
+      </c>
+      <c r="J7" t="n">
+        <v>104</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.1345453707542304</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.06362569240440749</v>
+      </c>
+      <c r="M7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>45071</v>
-      </c>
-      <c r="G7" t="n">
-        <v>350</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>-0.3268135676014448</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>-0.3268135676014448</v>
-      </c>
-      <c r="J7" t="n">
-        <v>349</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.1943317719820405</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.1299458877981737</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -4804,31 +4805,31 @@
       </c>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>-0.3268135676014448</v>
+        <v>-0.3121003427249629</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="W7" t="n">
-        <v>-65</v>
+        <v>27</v>
       </c>
       <c r="X7" t="b">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0.4854725999705787</v>
+        <v>0.4537003899104699</v>
       </c>
     </row>
     <row r="8">
@@ -4848,34 +4849,34 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>44026</v>
+      </c>
+      <c r="G8" t="n">
+        <v>101</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="J8" t="n">
+        <v>100</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.1310208562110952</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.06077869181898075</v>
+      </c>
+      <c r="M8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>45072</v>
-      </c>
-      <c r="G8" t="n">
-        <v>351</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="J8" t="n">
-        <v>350</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.1993947475706169</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.1335211970875572</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -4885,31 +4886,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="W8" t="n">
-        <v>-64</v>
+        <v>23</v>
       </c>
       <c r="X8" t="b">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0.4793846220779194</v>
+        <v>0.4325158389774153</v>
       </c>
     </row>
   </sheetData>
@@ -5097,6 +5098,741 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="G2" t="n">
+        <v>473</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="J2" t="n">
+        <v>472</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.1873955345996989</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.1456175032694574</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>253</v>
+      </c>
+      <c r="R2" t="n">
+        <v>58</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>220</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>0.4792042812088539</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>equal_weight</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>equal_t_10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>45089</v>
+      </c>
+      <c r="G3" t="n">
+        <v>361</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>-0.2880125431936822</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>-0.2880125431936822</v>
+      </c>
+      <c r="J3" t="n">
+        <v>360</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.1702003091096035</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.1155792312134959</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>195</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>-0.2880125431936822</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-0.2880125431936822</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>166</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-54</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>0.4045191252182836</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>44995</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>45344</v>
+      </c>
+      <c r="G4" t="n">
+        <v>536</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.298221368786892</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>-0.298221368786892</v>
+      </c>
+      <c r="J4" t="n">
+        <v>535</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.1869460824536023</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.1546210731632438</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>297</v>
+      </c>
+      <c r="R4" t="n">
+        <v>102</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>-0.298221368786892</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-0.298221368786892</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>239</v>
+      </c>
+      <c r="W4" t="n">
+        <v>19</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>0.4249507686937986</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>45121</v>
+      </c>
+      <c r="G5" t="n">
+        <v>383</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="J5" t="n">
+        <v>382</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.1328475678049171</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.09291469197671884</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>195</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>188</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-32</v>
+      </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0.3128225283655466</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>45054</v>
+      </c>
+      <c r="G6" t="n">
+        <v>337</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="J6" t="n">
+        <v>336</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.1702187018471014</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.1116942447466524</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>195</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-0.2944579323458331</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>142</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-78</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0.4173499297141365</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>45071</v>
+      </c>
+      <c r="G7" t="n">
+        <v>350</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="J7" t="n">
+        <v>349</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.1943317719820405</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.1299458877981737</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>195</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-0.3268135676014448</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>155</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-65</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0.4854725999705787</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>45072</v>
+      </c>
+      <c r="G8" t="n">
+        <v>351</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="J8" t="n">
+        <v>350</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.1993947475706169</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.1335211970875572</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>195</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>156</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-64</v>
+      </c>
+      <c r="X8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0.4793846220779194</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="E2" s="2" t="n">
